--- a/output/DTR_7-4_ALDUEZA_SJ.xlsx
+++ b/output/DTR_7-4_ALDUEZA_SJ.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="76">
   <si>
     <t>Republic of the Philippines</t>
   </si>
@@ -74,6 +74,18 @@
   </si>
   <si>
     <t>Minutes</t>
+  </si>
+  <si>
+    <t>Sunday</t>
+  </si>
+  <si>
+    <t>Saturday</t>
+  </si>
+  <si>
+    <t>Eid'l Fitr</t>
+  </si>
+  <si>
+    <t>Sunday / Palm Sunday</t>
   </si>
   <si>
     <t>Total</t>
@@ -1286,7 +1298,9 @@
       <c r="E19" s="7"/>
       <c r="F19" s="7"/>
       <c r="G19" s="7"/>
-      <c r="H19" s="23"/>
+      <c r="H19" s="23" t="s">
+        <v>18</v>
+      </c>
       <c r="I19" s="7"/>
       <c r="J19" s="7"/>
       <c r="K19" s="7"/>
@@ -1305,13 +1319,13 @@
         <v>2</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E20" s="7"/>
       <c r="F20" s="7"/>
@@ -1335,13 +1349,13 @@
         <v>3</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="E21" s="7"/>
       <c r="F21" s="7"/>
@@ -1365,10 +1379,10 @@
         <v>4</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
@@ -1393,13 +1407,13 @@
         <v>5</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E23" s="7"/>
       <c r="F23" s="7"/>
@@ -1423,13 +1437,13 @@
         <v>6</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E24" s="7"/>
       <c r="F24" s="7"/>
@@ -1458,7 +1472,9 @@
       <c r="E25" s="7"/>
       <c r="F25" s="7"/>
       <c r="G25" s="7"/>
-      <c r="H25" s="23"/>
+      <c r="H25" s="23" t="s">
+        <v>19</v>
+      </c>
       <c r="I25" s="7"/>
       <c r="J25" s="7"/>
       <c r="K25" s="7"/>
@@ -1482,7 +1498,9 @@
       <c r="E26" s="7"/>
       <c r="F26" s="7"/>
       <c r="G26" s="7"/>
-      <c r="H26" s="23"/>
+      <c r="H26" s="23" t="s">
+        <v>18</v>
+      </c>
       <c r="I26" s="7"/>
       <c r="J26" s="7"/>
       <c r="K26" s="7"/>
@@ -1501,13 +1519,13 @@
         <v>9</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="E27" s="7"/>
       <c r="F27" s="7"/>
@@ -1531,13 +1549,13 @@
         <v>10</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="E28" s="7"/>
       <c r="F28" s="7"/>
@@ -1561,13 +1579,13 @@
         <v>11</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="E29" s="7"/>
       <c r="F29" s="7"/>
@@ -1591,13 +1609,13 @@
         <v>12</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E30" s="7"/>
       <c r="F30" s="7"/>
@@ -1621,13 +1639,13 @@
         <v>13</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E31" s="7"/>
       <c r="F31" s="7"/>
@@ -1656,7 +1674,9 @@
       <c r="E32" s="7"/>
       <c r="F32" s="7"/>
       <c r="G32" s="7"/>
-      <c r="H32" s="23"/>
+      <c r="H32" s="23" t="s">
+        <v>19</v>
+      </c>
       <c r="I32" s="7"/>
       <c r="J32" s="7"/>
       <c r="K32" s="7"/>
@@ -1680,7 +1700,9 @@
       <c r="E33" s="7"/>
       <c r="F33" s="7"/>
       <c r="G33" s="7"/>
-      <c r="H33" s="23"/>
+      <c r="H33" s="23" t="s">
+        <v>18</v>
+      </c>
       <c r="I33" s="7"/>
       <c r="J33" s="7"/>
       <c r="K33" s="7"/>
@@ -1699,13 +1721,13 @@
         <v>16</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E34" s="7"/>
       <c r="F34" s="7"/>
@@ -1729,13 +1751,13 @@
         <v>17</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E35" s="7"/>
       <c r="F35" s="7"/>
@@ -1759,13 +1781,13 @@
         <v>18</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E36" s="7"/>
       <c r="F36" s="7"/>
@@ -1789,10 +1811,10 @@
         <v>19</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D37" s="7"/>
       <c r="E37" s="7"/>
@@ -1822,7 +1844,9 @@
       <c r="E38" s="7"/>
       <c r="F38" s="7"/>
       <c r="G38" s="7"/>
-      <c r="H38" s="23"/>
+      <c r="H38" s="23" t="s">
+        <v>20</v>
+      </c>
       <c r="I38" s="7"/>
       <c r="J38" s="7"/>
       <c r="K38" s="7"/>
@@ -1846,7 +1870,9 @@
       <c r="E39" s="8"/>
       <c r="F39" s="8"/>
       <c r="G39" s="8"/>
-      <c r="H39" s="23"/>
+      <c r="H39" s="23" t="s">
+        <v>19</v>
+      </c>
       <c r="I39" s="8"/>
       <c r="J39" s="8"/>
       <c r="K39" s="8"/>
@@ -1870,7 +1896,9 @@
       <c r="E40" s="7"/>
       <c r="F40" s="7"/>
       <c r="G40" s="7"/>
-      <c r="H40" s="23"/>
+      <c r="H40" s="23" t="s">
+        <v>18</v>
+      </c>
       <c r="I40" s="7"/>
       <c r="J40" s="7"/>
       <c r="K40" s="7"/>
@@ -1889,13 +1917,13 @@
         <v>23</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="E41" s="7"/>
       <c r="F41" s="7"/>
@@ -1913,13 +1941,13 @@
         <v>24</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E42" s="8"/>
       <c r="F42" s="8"/>
@@ -1955,13 +1983,13 @@
         <v>26</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E44" s="8"/>
       <c r="F44" s="8"/>
@@ -1979,13 +2007,13 @@
         <v>27</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E45" s="7"/>
       <c r="F45" s="7"/>
@@ -2008,7 +2036,9 @@
       <c r="E46" s="7"/>
       <c r="F46" s="7"/>
       <c r="G46" s="7"/>
-      <c r="H46" s="23"/>
+      <c r="H46" s="23" t="s">
+        <v>19</v>
+      </c>
       <c r="I46" s="7"/>
       <c r="J46" s="7"/>
       <c r="K46" s="7"/>
@@ -2026,7 +2056,9 @@
       <c r="E47" s="7"/>
       <c r="F47" s="7"/>
       <c r="G47" s="7"/>
-      <c r="H47" s="23"/>
+      <c r="H47" s="23" t="s">
+        <v>21</v>
+      </c>
       <c r="I47" s="7"/>
       <c r="J47" s="7"/>
       <c r="K47" s="7"/>
@@ -2039,10 +2071,10 @@
         <v>30</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D48" s="7"/>
       <c r="E48" s="7"/>
@@ -2076,7 +2108,7 @@
     </row>
     <row r="50" spans="1:20" s="7" customFormat="1">
       <c r="A50" s="25" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B50" s="7"/>
       <c r="C50" s="7"/>
@@ -2125,7 +2157,7 @@
     </row>
     <row r="52" spans="1:20" s="7" customFormat="1">
       <c r="A52" s="27" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B52" s="7"/>
       <c r="C52" s="7"/>
@@ -2149,7 +2181,7 @@
     </row>
     <row r="53" spans="1:20" s="7" customFormat="1">
       <c r="A53" s="7" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B53" s="7"/>
       <c r="C53" s="7"/>
@@ -2219,7 +2251,7 @@
     </row>
     <row r="56" spans="1:20" s="7" customFormat="1">
       <c r="A56" s="29" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B56" s="7"/>
       <c r="C56" s="7"/>
@@ -2265,7 +2297,7 @@
     </row>
     <row r="58" spans="1:20" s="7" customFormat="1">
       <c r="A58" s="30" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B58" s="7"/>
       <c r="C58" s="7"/>
@@ -2290,7 +2322,7 @@
     <row r="59" spans="1:20" s="7" customFormat="1">
       <c r="A59" s="7"/>
       <c r="B59" s="31" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C59" s="7"/>
       <c r="D59" s="7"/>
@@ -2335,7 +2367,7 @@
     </row>
     <row r="61" spans="1:20" s="7" customFormat="1">
       <c r="A61" s="32" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B61" s="7"/>
       <c r="C61" s="7"/>
@@ -2359,7 +2391,7 @@
     </row>
     <row r="62" spans="1:20" s="7" customFormat="1">
       <c r="A62" s="16" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B62" s="7"/>
       <c r="C62" s="7"/>
@@ -2490,47 +2522,47 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="3" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="4" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="3" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="3" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>

--- a/output/DTR_7-4_ALDUEZA_SJ.xlsx
+++ b/output/DTR_7-4_ALDUEZA_SJ.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="83">
   <si>
     <t>Republic of the Philippines</t>
   </si>
@@ -157,70 +157,91 @@
     <t>12:09</t>
   </si>
   <si>
+    <t>12:17</t>
+  </si>
+  <si>
+    <t>12:20</t>
+  </si>
+  <si>
+    <t>12:05</t>
+  </si>
+  <si>
+    <t>12:18</t>
+  </si>
+  <si>
+    <t>12:27</t>
+  </si>
+  <si>
+    <t>12:24</t>
+  </si>
+  <si>
+    <t>12:10</t>
+  </si>
+  <si>
+    <t>12:39</t>
+  </si>
+  <si>
+    <t>12:04</t>
+  </si>
+  <si>
+    <t>12:29</t>
+  </si>
+  <si>
+    <t>12:13</t>
+  </si>
+  <si>
+    <t>12:11</t>
+  </si>
+  <si>
     <t>16:11</t>
   </si>
   <si>
-    <t>12:17</t>
-  </si>
-  <si>
-    <t>12:20</t>
-  </si>
-  <si>
-    <t>12:05</t>
-  </si>
-  <si>
-    <t>12:18</t>
-  </si>
-  <si>
-    <t>12:27</t>
-  </si>
-  <si>
-    <t>12:24</t>
+    <t>12:19</t>
+  </si>
+  <si>
+    <t>12:21</t>
+  </si>
+  <si>
+    <t>12:06</t>
+  </si>
+  <si>
+    <t>12:22</t>
+  </si>
+  <si>
+    <t>12:26</t>
   </si>
   <si>
     <t>16:05</t>
   </si>
   <si>
-    <t>12:10</t>
-  </si>
-  <si>
-    <t>12:39</t>
-  </si>
-  <si>
-    <t>12:04</t>
-  </si>
-  <si>
-    <t>12:29</t>
+    <t>12:40</t>
+  </si>
+  <si>
+    <t>12:30</t>
   </si>
   <si>
     <t>16:00</t>
   </si>
   <si>
-    <t>12:13</t>
-  </si>
-  <si>
-    <t>12:11</t>
-  </si>
-  <si>
-    <t>12:19</t>
-  </si>
-  <si>
-    <t>12:21</t>
-  </si>
-  <si>
-    <t>12:06</t>
-  </si>
-  <si>
-    <t>12:22</t>
-  </si>
-  <si>
-    <t>12:26</t>
-  </si>
-  <si>
-    <t>12:40</t>
-  </si>
-  <si>
-    <t>12:30</t>
+    <t>16:03</t>
+  </si>
+  <si>
+    <t>16:06</t>
+  </si>
+  <si>
+    <t>16:02</t>
+  </si>
+  <si>
+    <t>16:01</t>
+  </si>
+  <si>
+    <t>16:07</t>
+  </si>
+  <si>
+    <t>16:09</t>
+  </si>
+  <si>
+    <t>16:20</t>
   </si>
   <si>
     <t>on Forced/Mandatory Leave</t>
@@ -1325,9 +1346,11 @@
         <v>43</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="E20" s="7"/>
+        <v>55</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>67</v>
+      </c>
       <c r="F20" s="7"/>
       <c r="G20" s="7"/>
       <c r="H20" s="7"/>
@@ -1355,9 +1378,11 @@
         <v>44</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="E21" s="7"/>
+        <v>56</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>68</v>
+      </c>
       <c r="F21" s="7"/>
       <c r="G21" s="7"/>
       <c r="H21" s="7"/>
@@ -1381,10 +1406,10 @@
       <c r="B22" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="C22" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="D22" s="8"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="8" t="s">
+        <v>57</v>
+      </c>
       <c r="E22" s="8"/>
       <c r="F22" s="8"/>
       <c r="G22" s="8"/>
@@ -1410,12 +1435,14 @@
         <v>33</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="E23" s="7"/>
+        <v>58</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>69</v>
+      </c>
       <c r="F23" s="7"/>
       <c r="G23" s="7"/>
       <c r="H23" s="7"/>
@@ -1440,12 +1467,14 @@
         <v>34</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="E24" s="7"/>
+        <v>59</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>66</v>
+      </c>
       <c r="F24" s="7"/>
       <c r="G24" s="7"/>
       <c r="H24" s="7"/>
@@ -1522,12 +1551,14 @@
         <v>35</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="E27" s="7"/>
+        <v>60</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>69</v>
+      </c>
       <c r="F27" s="7"/>
       <c r="G27" s="7"/>
       <c r="H27" s="7"/>
@@ -1552,10 +1583,10 @@
         <v>34</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E28" s="7"/>
       <c r="F28" s="7"/>
@@ -1582,12 +1613,14 @@
         <v>36</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="E29" s="7"/>
+        <v>54</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>69</v>
+      </c>
       <c r="F29" s="7"/>
       <c r="G29" s="7"/>
       <c r="H29" s="7"/>
@@ -1612,12 +1645,14 @@
         <v>34</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="E30" s="7"/>
+        <v>58</v>
+      </c>
+      <c r="E30" s="7" t="s">
+        <v>70</v>
+      </c>
       <c r="F30" s="7"/>
       <c r="G30" s="7"/>
       <c r="H30" s="7"/>
@@ -1642,12 +1677,14 @@
         <v>32</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="E31" s="7"/>
+        <v>59</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>66</v>
+      </c>
       <c r="F31" s="7"/>
       <c r="G31" s="7"/>
       <c r="H31" s="7"/>
@@ -1724,12 +1761,14 @@
         <v>37</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="E34" s="7"/>
+        <v>62</v>
+      </c>
+      <c r="E34" s="7" t="s">
+        <v>70</v>
+      </c>
       <c r="F34" s="7"/>
       <c r="G34" s="7"/>
       <c r="H34" s="7"/>
@@ -1757,9 +1796,11 @@
         <v>43</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="E35" s="7"/>
+        <v>55</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>63</v>
+      </c>
       <c r="F35" s="7"/>
       <c r="G35" s="7"/>
       <c r="H35" s="7"/>
@@ -1784,12 +1825,14 @@
         <v>39</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="E36" s="7"/>
+        <v>58</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>71</v>
+      </c>
       <c r="F36" s="7"/>
       <c r="G36" s="7"/>
       <c r="H36" s="7"/>
@@ -1813,10 +1856,10 @@
       <c r="B37" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="C37" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="D37" s="7"/>
+      <c r="C37" s="7"/>
+      <c r="D37" s="7" t="s">
+        <v>63</v>
+      </c>
       <c r="E37" s="7"/>
       <c r="F37" s="7"/>
       <c r="G37" s="7"/>
@@ -1920,12 +1963,14 @@
         <v>37</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="E41" s="7"/>
+        <v>56</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>71</v>
+      </c>
       <c r="F41" s="7"/>
       <c r="G41" s="7"/>
       <c r="H41" s="7"/>
@@ -1944,12 +1989,14 @@
         <v>37</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="E42" s="8"/>
+        <v>64</v>
+      </c>
+      <c r="E42" s="8" t="s">
+        <v>70</v>
+      </c>
       <c r="F42" s="8"/>
       <c r="G42" s="8"/>
       <c r="H42" s="8"/>
@@ -1986,12 +2033,14 @@
         <v>41</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="E44" s="8"/>
+        <v>47</v>
+      </c>
+      <c r="E44" s="8" t="s">
+        <v>72</v>
+      </c>
       <c r="F44" s="8"/>
       <c r="G44" s="8"/>
       <c r="H44" s="8"/>
@@ -2010,12 +2059,14 @@
         <v>39</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="E45" s="7"/>
+        <v>65</v>
+      </c>
+      <c r="E45" s="7" t="s">
+        <v>73</v>
+      </c>
       <c r="F45" s="7"/>
       <c r="G45" s="7"/>
       <c r="H45" s="7"/>
@@ -2073,10 +2124,10 @@
       <c r="B48" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="C48" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="D48" s="7"/>
+      <c r="C48" s="7"/>
+      <c r="D48" s="7" t="s">
+        <v>66</v>
+      </c>
       <c r="E48" s="7"/>
       <c r="F48" s="7"/>
       <c r="G48" s="7"/>
@@ -2522,47 +2573,47 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="2" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="2" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="2" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="2" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="3" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="2" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="4" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="3" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="3" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>
